--- a/adapters/mop-ops-assistant/templates/search-recommend-material-template.xlsx
+++ b/adapters/mop-ops-assistant/templates/search-recommend-material-template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写任务" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="填写任务" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'填写任务'!$A$1:$G$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'字段说明'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'填写任务'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'字段说明'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,17 +465,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="88" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="88" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -486,35 +487,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>商家编码</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>素材图片</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>素材张数</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>添加标题</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>内容描述</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>裁剪比例</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
@@ -526,31 +532,36 @@
           <t>1051467606993</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>455133A2114Z</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>亚麻连衣裙穿搭</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合，突出自然垂坠和轻盈气质。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>3:4</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>示例：素材图片可留空，在 UI 选择素材根目录后读取 商品ID/01.jpg 到 03.jpg</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>示例：素材图片可留空，在 UI 选择业务图包根目录后，按商家编码自动读取 图片/主图/达人 下的前 3 张</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>搜推图文素材要求至少 3 张图片，最多 9 张图片。
 添加标题必填，上限 20 个中文字符；内容描述必填，上限 1000 个中文字符。</t>
@@ -565,36 +576,43 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>564231A5355Z</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>/Users/you/Desktop/搜推素材/776047586897/01.jpg;/Users/you/Desktop/搜推素材/776047586897/02.jpg;/Users/you/Desktop/搜推素材/776047586897/03.jpg</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>凉感Polo上新</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>轻薄凉感面料适合夏季穿着，版型利落不闷热，适合通勤、休闲和日常搭配。</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>示例：直接填写三张图片路径</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>素材图片可写本地绝对路径或 http(s) URL；多张可用换行、分号、竖线或空格分隔。
-素材根目录约定：素材根目录/商品ID/01.jpg、02.jpg、03.jpg。
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>商品ID和商家编码二选一必填；商品ID为空时，脚本会自动按商家编码去千牛“我的商品”解析商品ID。
+素材图片可写本地绝对路径或 http(s) URL；多张可用换行、分号、竖线或空格分隔。
+业务图包约定：素材根目录/含商家编码的商品文件夹/图片/主图/达人/图片；顶层目录可用 + 关联多个商家编码。
+未匹配业务图包时，兼容旧规则：素材根目录/商品ID或商家编码/01.jpg、02.jpg、03.jpg。
 上传前会自动居中裁剪到 3:4 或 1:1；单行“裁剪比例”列可覆盖运行界面默认值。
-手动多选命名约定：商品ID_01.jpg，或父文件夹名为商品ID。</t>
+手动多选命名约定：商品ID_01.jpg 或 商家编码_01.jpg，或父文件夹名为商品ID/商家编码。</t>
         </is>
       </c>
     </row>
@@ -604,9 +622,10 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -614,9 +633,10 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -624,9 +644,10 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -634,9 +655,10 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -644,9 +666,10 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -654,9 +677,10 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -664,9 +688,10 @@
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -674,9 +699,10 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="n"/>
@@ -684,9 +710,10 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="3" t="n"/>
       <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="n"/>
@@ -694,9 +721,10 @@
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="n"/>
@@ -704,9 +732,10 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="n"/>
@@ -714,9 +743,10 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="2" t="n"/>
@@ -724,9 +754,10 @@
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="3" t="n"/>
       <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="n"/>
@@ -734,9 +765,10 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="2" t="n"/>
@@ -744,9 +776,10 @@
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="3" t="n"/>
       <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="2" t="n"/>
@@ -754,9 +787,10 @@
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="3" t="n"/>
       <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="n"/>
@@ -764,9 +798,10 @@
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="3" t="n"/>
       <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2" t="n"/>
@@ -774,9 +809,10 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="3" t="n"/>
       <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="n"/>
@@ -784,9 +820,10 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="2" t="n"/>
@@ -794,9 +831,10 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="3" t="n"/>
       <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="2" t="n"/>
@@ -804,9 +842,10 @@
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="3" t="n"/>
       <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="2" t="n"/>
@@ -814,9 +853,10 @@
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="n"/>
@@ -824,9 +864,10 @@
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="3" t="n"/>
       <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -834,9 +875,10 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="3" t="n"/>
       <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="2" t="n"/>
@@ -844,9 +886,10 @@
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="2" t="n"/>
@@ -854,9 +897,10 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="2" t="n"/>
@@ -864,14 +908,15 @@
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="3" t="n"/>
       <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:H30"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="裁剪比例填写错误" error="裁剪比例仅支持 3:4 或 1:1" promptTitle="裁剪比例" prompt="请选择 3:4 或 1:1；留空则使用运行界面默认值。" type="list">
+    <dataValidation sqref="G2:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="裁剪比例填写错误" error="裁剪比例仅支持 3:4 或 1:1" promptTitle="裁剪比例" prompt="请选择 3:4 或 1:1；留空则使用运行界面默认值。" type="list">
       <formula1>"3:4,1:1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -885,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -924,12 +969,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>二选一</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>千牛/淘宝商品 ID；脚本会将图文素材关联到该商品</t>
+          <t>千牛/淘宝商品 ID；有值时优先使用。为空但填写商家编码时，脚本会自动解析商品ID</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -941,29 +986,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>素材图片</t>
+          <t>商家编码</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>二选一</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>本地绝对路径或 http(s) 图片 URL；多张用换行、分号、竖线或空格分隔。也可以留空，改在 UI 选择素材根目录或手动多选素材图片</t>
+          <t>店铺内部商家编码；商品ID为空时，脚本会去千牛“我的商品”按商家编码搜索并取回商品ID</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>/Users/you/Desktop/搜推素材/1051467606993/01.jpg;/Users/you/Desktop/搜推素材/1051467606993/02.jpg;/Users/you/Desktop/搜推素材/1051467606993/03.jpg</t>
+          <t>455133A2114Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>素材张数</t>
+          <t>素材图片</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -973,41 +1018,41 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>素材图片为空且填写了“素材根目录”时生效；搜推图文至少 3 张、最多 9 张</t>
+          <t>本地绝对路径或 http(s) 图片 URL；多张用换行、分号、竖线或空格分隔。也可以留空，改在 UI 选择素材根目录或手动多选素材图片</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>/Users/you/Desktop/搜推素材/1051467606993/01.jpg;/Users/you/Desktop/搜推素材/1051467606993/02.jpg;/Users/you/Desktop/搜推素材/1051467606993/03.jpg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>添加标题</t>
+          <t>素材张数</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>发布弹窗里的“添加标题”；必填，上限 20 个中文字符；页面建议 8-10 个中文字符</t>
+          <t>素材图片为空且填写了“素材根目录”时生效；业务图包按顺序取 图片/主图/达人 下前 N 张；搜推图文至少 3 张、最多 9 张</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>亚麻连衣裙穿搭</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>内容描述</t>
+          <t>添加标题</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1017,41 +1062,41 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>发布弹窗里的“内容描述”；必填，上限 1000 个中文字符；页面建议 10-1000 个中文字符</t>
+          <t>发布弹窗里的“添加标题”；必填，上限 20 个中文字符；页面建议 8-10 个中文字符</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合。</t>
+          <t>亚麻连衣裙穿搭</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>裁剪比例</t>
+          <t>内容描述</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>上传前自动居中裁剪；支持 3:4 或 1:1；留空使用运行界面的默认裁剪比例</t>
+          <t>发布弹窗里的“内容描述”；必填，上限 1000 个中文字符；页面建议 10-1000 个中文字符</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3:4</t>
+          <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>裁剪比例</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1061,61 +1106,83 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>原样带到结果里，便于人工追踪</t>
+          <t>上传前自动居中裁剪；支持 3:4 或 1:1；留空使用运行界面的默认裁剪比例</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>第一批搜推素材</t>
+          <t>3:4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>素材包摆放</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>使用素材根目录时按“素材根目录/商品ID/01.jpg、02.jpg、03.jpg”摆放；扩展名固定为 jpg；png/jpeg/webp 请写入素材图片列或手动多选</t>
+          <t>原样带到结果里，便于人工追踪</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>/Users/you/Desktop/搜推素材/1051467606993/01.jpg</t>
+          <t>第一批搜推素材</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>素材包摆放</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>推荐业务图包：素材根目录/MOP655137Z4106Z+656939D1213Y/图片/主图/达人/图片；顶层目录可用 + 关联多个商家编码；脚本只取主图图片，忽略视频和买家秀</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>/Users/you/Desktop/搜推素材/MOP655137Z4106Z+656939D1213Y/图片/主图/AHOYECHO/xxx.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>手动多选命名</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>使用“手动选择素材图片”时，文件名以商品ID开头或父文件夹为商品ID；脚本会按商品ID自动归组</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1051467606993_01.jpg 或 1051467606993/01.jpg</t>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>使用“手动选择素材图片”时，文件名以商品ID/商家编码开头或父文件夹为商品ID/商家编码；脚本会自动归组</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>455133A2114Z_01.jpg 或 455133A2114Z/01.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/adapters/mop-ops-assistant/templates/search-recommend-material-template.xlsx
+++ b/adapters/mop-ops-assistant/templates/search-recommend-material-template.xlsx
@@ -11,8 +11,8 @@
     <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'填写任务'!$A$1:$H$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'字段说明'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'填写任务'!$A$1:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'字段说明'!$A$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,18 +465,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
-    <col width="88" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="92" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -492,35 +493,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>达人</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>素材图片</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>素材张数</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>添加标题</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>内容描述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>裁剪比例</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
@@ -538,37 +544,38 @@
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>亚麻连衣裙穿搭</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合，突出自然垂坠和轻盈气质。</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>3:4</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>示例：素材图片可留空，在 UI 选择业务图包根目录后，按商家编码自动读取 图片/主图/达人 下的前 3 张</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>示例：素材图片可留空；同款单行会按主图下每个达人文件夹各发布一条；同款多行会按行顺序分配达人包，保留每行标题/描述</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>搜推图文素材要求至少 3 张图片，最多 9 张图片。
 添加标题必填，上限 20 个中文字符；内容描述必填，上限 1000 个中文字符。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="86" customHeight="1">
+    <row r="3" ht="102" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>776047586897</t>
@@ -581,35 +588,43 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>达人A</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>/Users/you/Desktop/搜推素材/776047586897/01.jpg;/Users/you/Desktop/搜推素材/776047586897/02.jpg;/Users/you/Desktop/搜推素材/776047586897/03.jpg</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>凉感Polo上新</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>轻薄凉感面料适合夏季穿着，版型利落不闷热，适合通勤、休闲和日常搭配。</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>示例：直接填写三张图片路径</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>商品ID和商家编码二选一必填；商品ID为空时，脚本会自动按商家编码去千牛“我的商品”解析商品ID。
 素材图片可写本地绝对路径或 http(s) URL；多张可用换行、分号、竖线或空格分隔。
 业务图包约定：素材根目录/含商家编码的商品文件夹/图片/主图/达人/图片；顶层目录可用 + 关联多个商家编码。
+如果同款只填一行，脚本会按主图下的每个达人文件夹拆成多条内容，每个达人文件夹各取前 N 张素材。
+如果同款在表格里填写多行，脚本会按行顺序分配达人图片包；每行自己的标题、内容描述、裁剪比例、备注会保留。
+可选填写“达人”列精确指定达人文件夹名。
 未匹配业务图包时，兼容旧规则：素材根目录/商品ID或商家编码/01.jpg、02.jpg、03.jpg。
 上传前会自动居中裁剪到 3:4 或 1:1；单行“裁剪比例”列可覆盖运行界面默认值。
 手动多选命名约定：商品ID_01.jpg 或 商家编码_01.jpg，或父文件夹名为商品ID/商家编码。</t>
@@ -623,9 +638,10 @@
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="3" t="n"/>
       <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -634,9 +650,10 @@
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -645,9 +662,10 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="3" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -656,9 +674,10 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="3" t="n"/>
       <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -667,9 +686,10 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="3" t="n"/>
       <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -678,9 +698,10 @@
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="3" t="n"/>
       <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -689,9 +710,10 @@
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -700,9 +722,10 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="3" t="n"/>
       <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2" t="n"/>
@@ -711,9 +734,10 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="3" t="n"/>
       <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="n"/>
@@ -722,9 +746,10 @@
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="3" t="n"/>
       <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="2" t="n"/>
@@ -733,9 +758,10 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="n"/>
@@ -744,9 +770,10 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="3" t="n"/>
       <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="2" t="n"/>
@@ -755,9 +782,10 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="n"/>
@@ -766,9 +794,10 @@
       <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="3" t="n"/>
       <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="2" t="n"/>
@@ -777,9 +806,10 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="3" t="n"/>
       <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="2" t="n"/>
@@ -788,9 +818,10 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="2" t="n"/>
@@ -799,9 +830,10 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="3" t="n"/>
       <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2" t="n"/>
@@ -810,9 +842,10 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="3" t="n"/>
       <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="2" t="n"/>
@@ -821,9 +854,10 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="3" t="n"/>
       <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="2" t="n"/>
@@ -832,9 +866,10 @@
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="2" t="n"/>
@@ -843,9 +878,10 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="3" t="n"/>
       <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="2" t="n"/>
@@ -854,9 +890,10 @@
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="3" t="n"/>
       <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="n"/>
@@ -865,9 +902,10 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="3" t="n"/>
       <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -876,9 +914,10 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="3" t="n"/>
       <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="2" t="n"/>
@@ -887,9 +926,10 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="3" t="n"/>
       <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="2" t="n"/>
@@ -898,9 +938,10 @@
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="3" t="n"/>
       <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="2" t="n"/>
@@ -909,14 +950,15 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="3" t="n"/>
       <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:I30"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="裁剪比例填写错误" error="裁剪比例仅支持 3:4 或 1:1" promptTitle="裁剪比例" prompt="请选择 3:4 或 1:1；留空则使用运行界面默认值。" type="list">
+    <dataValidation sqref="H2:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="裁剪比例填写错误" error="裁剪比例仅支持 3:4 或 1:1" promptTitle="裁剪比例" prompt="请选择 3:4 或 1:1；留空则使用运行界面默认值。" type="list">
       <formula1>"3:4,1:1"</formula1>
     </dataValidation>
   </dataValidations>
@@ -930,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1008,7 +1050,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>素材图片</t>
+          <t>达人</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1018,19 +1060,19 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>本地绝对路径或 http(s) 图片 URL；多张用换行、分号、竖线或空格分隔。也可以留空，改在 UI 选择素材根目录或手动多选素材图片</t>
+          <t>填写业务图包主图下的达人文件夹名时，会精确使用该达人图片包；不填时，单行同款会展开全部达人，多行重复同款会按行顺序分配达人包</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>/Users/you/Desktop/搜推素材/1051467606993/01.jpg;/Users/you/Desktop/搜推素材/1051467606993/02.jpg;/Users/you/Desktop/搜推素材/1051467606993/03.jpg</t>
+          <t>AHOYECHO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>素材张数</t>
+          <t>素材图片</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1040,41 +1082,41 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>素材图片为空且填写了“素材根目录”时生效；业务图包按顺序取 图片/主图/达人 下前 N 张；搜推图文至少 3 张、最多 9 张</t>
+          <t>本地绝对路径或 http(s) 图片 URL；多张用换行、分号、竖线或空格分隔。也可以留空，改在 UI 选择素材根目录或手动多选素材图片</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>/Users/you/Desktop/搜推素材/1051467606993/01.jpg;/Users/you/Desktop/搜推素材/1051467606993/02.jpg;/Users/you/Desktop/搜推素材/1051467606993/03.jpg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>添加标题</t>
+          <t>素材张数</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>发布弹窗里的“添加标题”；必填，上限 20 个中文字符；页面建议 8-10 个中文字符</t>
+          <t>素材图片为空且填写了“素材根目录”时生效；单行同款展开全部达人，多行重复同款按行顺序分配达人包；每条取对应达人前 N 张；搜推图文至少 3 张、最多 9 张</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>亚麻连衣裙穿搭</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>内容描述</t>
+          <t>添加标题</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1084,41 +1126,41 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>发布弹窗里的“内容描述”；必填，上限 1000 个中文字符；页面建议 10-1000 个中文字符</t>
+          <t>发布弹窗里的“添加标题”；必填，上限 20 个中文字符；页面建议 8-10 个中文字符</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合。</t>
+          <t>亚麻连衣裙穿搭</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>裁剪比例</t>
+          <t>内容描述</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>上传前自动居中裁剪；支持 3:4 或 1:1；留空使用运行界面的默认裁剪比例</t>
+          <t>发布弹窗里的“内容描述”；必填，上限 1000 个中文字符；页面建议 10-1000 个中文字符</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3:4</t>
+          <t>清爽亚麻质感搭配简洁版型，日常通勤和周末出游都很适合。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>裁剪比例</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1128,61 +1170,83 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>原样带到结果里，便于人工追踪</t>
+          <t>上传前自动居中裁剪；支持 3:4 或 1:1；留空使用运行界面的默认裁剪比例</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>第一批搜推素材</t>
+          <t>3:4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>素材包摆放</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>推荐业务图包：素材根目录/MOP655137Z4106Z+656939D1213Y/图片/主图/达人/图片；顶层目录可用 + 关联多个商家编码；脚本只取主图图片，忽略视频和买家秀</t>
+          <t>原样带到结果里，便于人工追踪</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>/Users/you/Desktop/搜推素材/MOP655137Z4106Z+656939D1213Y/图片/主图/AHOYECHO/xxx.jpg</t>
+          <t>第一批搜推素材</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>素材包摆放</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>推荐业务图包：素材根目录/MOP655137Z4106Z+656939D1213Y/图片/主图/达人/图片；顶层目录可用 + 关联多个商家编码；脚本只取主图图片，忽略视频和买家秀；多个达人文件夹可自动展开或按重复行分配</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>/Users/you/Desktop/搜推素材/MOP655137Z4106Z+656939D1213Y/图片/主图/AHOYECHO/xxx.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>手动多选命名</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>建议</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>使用“手动选择素材图片”时，文件名以商品ID/商家编码开头或父文件夹为商品ID/商家编码；脚本会自动归组</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>455133A2114Z_01.jpg 或 455133A2114Z/01.jpg</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D11"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>